--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Ï€ u Ï„Ñ�Ï„</t>
+          <t>L69: stray/suspicious non-ASCII glyph(s): U+96EA CJK UNIFIED IDEOGRAPH-96EA | isolated marker/symbol line :: 雪</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tween common and special injunctions, see Danielâ€™s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ground th</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ground th</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L29: isolated marker/symbol line :: s</t>
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -658,14 +662,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Ï€ jun Ñ�Ï„ ions.</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: common injunctions :â€”</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: of answer, on or after the expiration of fourteen days from•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -713,16 +713,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: lays from the service of the subpo Ã¦ ena;</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: of answer, on or after the expiration of fourteen days fromâ€¢</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -754,12 +746,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -774,7 +766,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 5</t>
+          <t>L69: stray/suspicious non-ASCII glyph(s): U+96EA CJK UNIFIED IDEOGRAPH-96EA | isolated marker/symbol line :: 雪</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -821,7 +813,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 8</t>
+          <t>L105: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -862,7 +854,11 @@
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L106: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr"/>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
@@ -961,12 +957,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1005,7 +1001,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1039,7 +1035,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
